--- a/results/components/gene_names/p4s5.xlsx
+++ b/results/components/gene_names/p4s5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>gene1</t>
   </si>
@@ -22,130 +22,142 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>dom</t>
-  </si>
-  <si>
-    <t>mbl</t>
-  </si>
-  <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>Pcaf</t>
-  </si>
-  <si>
-    <t>loco</t>
+    <t>Tina-1</t>
+  </si>
+  <si>
+    <t>MED24</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>SelG</t>
+  </si>
+  <si>
+    <t>cnc</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>foxo</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>kis</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Yp1</t>
+  </si>
+  <si>
+    <t>rdo</t>
+  </si>
+  <si>
+    <t>trc</t>
   </si>
   <si>
     <t>18w</t>
   </si>
   <si>
-    <t>Cks30A</t>
-  </si>
-  <si>
-    <t>Lis-1</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>Fas3</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>dmt</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>tok</t>
+    <t>yrt</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -554,82 +566,82 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -662,6 +674,22 @@
       </c>
       <c r="B23" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/results/components/gene_names/p4s5.xlsx
+++ b/results/components/gene_names/p4s5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>gene1</t>
   </si>
@@ -22,142 +22,70 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Tina-1</t>
-  </si>
-  <si>
-    <t>MED24</t>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>puc</t>
+  </si>
+  <si>
+    <t>tra2</t>
+  </si>
+  <si>
+    <t>by</t>
   </si>
   <si>
     <t>sgg</t>
   </si>
   <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Bap60</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>SelD</t>
-  </si>
-  <si>
-    <t>CkIIalpha</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>SelG</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>numb</t>
-  </si>
-  <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>tld</t>
-  </si>
-  <si>
-    <t>Dad</t>
-  </si>
-  <si>
-    <t>foxo</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>Lac</t>
-  </si>
-  <si>
-    <t>kis</t>
-  </si>
-  <si>
-    <t>Sry-delta</t>
-  </si>
-  <si>
-    <t>boss</t>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>pbl</t>
+  </si>
+  <si>
+    <t>wls</t>
+  </si>
+  <si>
+    <t>CG33205</t>
+  </si>
+  <si>
+    <t>Set2</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>Wnt5</t>
+  </si>
+  <si>
+    <t>chp</t>
   </si>
   <si>
     <t>Tm1</t>
   </si>
   <si>
-    <t>chic</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>Pgant35A</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>Yp1</t>
-  </si>
-  <si>
-    <t>rdo</t>
-  </si>
-  <si>
-    <t>trc</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>yrt</t>
-  </si>
-  <si>
-    <t>Hs6st</t>
+    <t>hep</t>
+  </si>
+  <si>
+    <t>ftz-f1</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>gbb</t>
+  </si>
+  <si>
+    <t>Jafrac2</t>
+  </si>
+  <si>
+    <t>ninaE</t>
   </si>
 </sst>
 </file>
@@ -489,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -513,183 +441,119 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
